--- a/Data/GrabSample_data/RI25-endmembers.xlsx
+++ b/Data/GrabSample_data/RI25-endmembers.xlsx
@@ -5,15 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="original" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Wade" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Hungerford" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Hungerford!$B$1:$B$76</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Wade!$B$1:$B$76</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="257">
   <si>
     <t xml:space="preserve">Sample ID</t>
   </si>
@@ -802,9 +804,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -870,12 +873,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -901,6 +908,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -6425,12 +6436,5415 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:AI76"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="8.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="8.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="0" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="7.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="28" style="0" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="21.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="33" style="0" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="17.98"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>7.295</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>28.341</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>297.517</v>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="Q2" s="0" t="n">
+        <v>65.519</v>
+      </c>
+      <c r="Y2" s="0" t="n">
+        <v>-72.169</v>
+      </c>
+      <c r="Z2" s="0" t="n">
+        <v>-10.467</v>
+      </c>
+      <c r="AE2" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>3.322</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>3.412</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>27.861</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <v>43.261</v>
+      </c>
+      <c r="Y3" s="0" t="n">
+        <v>-74.789</v>
+      </c>
+      <c r="Z3" s="0" t="n">
+        <v>-11.023</v>
+      </c>
+      <c r="AE3" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.0280914050177682</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0.0341624315975675</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0.0119220644732937</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>6.89782575598375</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>3.17502287026636</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>0.0252594593839047</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>12.3245356494279</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>25.117532506696</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>0.0080212294045925</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>36.9602816211563</v>
+      </c>
+      <c r="AE4" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" s="0" t="n">
+        <v>0.0191688595280883</v>
+      </c>
+      <c r="AG4" s="0" t="n">
+        <v>10.1481292662102</v>
+      </c>
+      <c r="AH4" s="0" t="n">
+        <v>0.201463056287082</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.0456121842968216</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0.0097109794719291</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0.0308215827195021</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>5.2538413868656</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>2.64189597846027</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>0.0213970033105503</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>7.26256562613223</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>14.3005759594319</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>0.0151832160409502</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>36.5368991902387</v>
+      </c>
+      <c r="AE5" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF5" s="0" t="n">
+        <v>0.0137520070283557</v>
+      </c>
+      <c r="AG5" s="0" t="n">
+        <v>5.60118951510513</v>
+      </c>
+      <c r="AH5" s="0" t="n">
+        <v>0.168031097528127</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.0716753261984213</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0.005710388901655</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0.0285237920091213</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>4.97724536484027</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>3.63005629729263</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>0.0365255565750062</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>5.96337648355687</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <v>12.6028583837091</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>0.0426538102070597</v>
+      </c>
+      <c r="Q6" s="0" t="n">
+        <v>28.8306144289319</v>
+      </c>
+      <c r="Y6" s="0" t="n">
+        <v>-103.78</v>
+      </c>
+      <c r="Z6" s="0" t="n">
+        <v>-14.592</v>
+      </c>
+      <c r="AE6" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF6" s="0" t="n">
+        <v>0.0128069990670046</v>
+      </c>
+      <c r="AG6" s="0" t="n">
+        <v>3.948961896738</v>
+      </c>
+      <c r="AH6" s="0" t="n">
+        <v>0.13035399555211</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.0451627246817397</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0.0367619497752374</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0.0030386312835831</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>5.3571778345676</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>2.58393060343014</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>0.0355282920737053</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>7.70166989951656</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <v>20.2961769254978</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>0.0135534395860428</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>41.1289967308976</v>
+      </c>
+      <c r="Y7" s="0" t="n">
+        <v>-104.173</v>
+      </c>
+      <c r="Z7" s="0" t="n">
+        <v>-15.105</v>
+      </c>
+      <c r="AE7" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF7" s="0" t="n">
+        <v>0.0151443755531104</v>
+      </c>
+      <c r="AG7" s="0" t="n">
+        <v>5.46730329024485</v>
+      </c>
+      <c r="AH7" s="0" t="n">
+        <v>0.185374172020883</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0.0521556625622279</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0.0667871118135</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0.0283190005295499</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>7.13254710558054</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>3.40306170328707</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>0.0336988133128507</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>10.4075552890786</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <v>22.9455859683735</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>0.0104884810746512</v>
+      </c>
+      <c r="Q8" s="0" t="n">
+        <v>53.1888916630217</v>
+      </c>
+      <c r="S8" s="0" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AE8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF8" s="0" t="n">
+        <v>0.0198865760694454</v>
+      </c>
+      <c r="AG8" s="0" t="n">
+        <v>8.73665802128005</v>
+      </c>
+      <c r="AH8" s="0" t="n">
+        <v>0.259503540703184</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0.0118693726109697</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0.178426551059082</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0.0184149910469105</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>8.08038343275131</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>3.22948502841281</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>0.0351463076121462</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>17.5123092232937</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <v>221.722281566804</v>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>0.0066565897948343</v>
+      </c>
+      <c r="Q9" s="0" t="n">
+        <v>55.4347035381111</v>
+      </c>
+      <c r="S9" s="0" t="n">
+        <v>389.777</v>
+      </c>
+      <c r="Y9" s="0" t="n">
+        <v>-71.444</v>
+      </c>
+      <c r="Z9" s="0" t="n">
+        <v>-10.547</v>
+      </c>
+      <c r="AE9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF9" s="0" t="n">
+        <v>0.0299616326728005</v>
+      </c>
+      <c r="AG9" s="0" t="n">
+        <v>7.76991371722743</v>
+      </c>
+      <c r="AH9" s="0" t="n">
+        <v>0.244557802849846</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0.0179110127698245</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0.035389203283852</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0.0045539327620859</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>8.49867497622398</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>3.23519431286504</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>0.0316227191874852</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>11.8028895283741</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <v>55.5407828111041</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>0.0065641525502455</v>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <v>57.8103283209994</v>
+      </c>
+      <c r="S10" s="0" t="n">
+        <v>36.24354745</v>
+      </c>
+      <c r="Y10" s="0" t="n">
+        <v>-70.493</v>
+      </c>
+      <c r="Z10" s="0" t="n">
+        <v>-10.48</v>
+      </c>
+      <c r="AE10" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF10" s="0" t="n">
+        <v>0.0245098603886824</v>
+      </c>
+      <c r="AG10" s="0" t="n">
+        <v>9.13284240712454</v>
+      </c>
+      <c r="AH10" s="0" t="n">
+        <v>0.268574211597268</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0.0076376620462609</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0.0016663384819432</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0.0571509565142312</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>4.09138987053165</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>0.218635949190643</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <v>0.0025128400915795</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <v>0.60244190923028</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <v>0.717976300296246</v>
+      </c>
+      <c r="P11" s="0" t="n">
+        <v>0.0126674720900835</v>
+      </c>
+      <c r="Q11" s="0" t="n">
+        <v>4.03730185244424</v>
+      </c>
+      <c r="Y11" s="0" t="n">
+        <v>-78.977</v>
+      </c>
+      <c r="Z11" s="0" t="n">
+        <v>-12.013</v>
+      </c>
+      <c r="AE11" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF11" s="0" t="n">
+        <v>0.0039839168002378</v>
+      </c>
+      <c r="AG11" s="0" t="n">
+        <v>1.15697566815387</v>
+      </c>
+      <c r="AH11" s="0" t="n">
+        <v>0.0237166572146709</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>0.0156627154284537</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>0.0028972413170145</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>0.0185145677339779</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>4.14724129717971</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>0.315981964013072</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <v>0.0050014722053655</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <v>0.633652646520205</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <v>0.631484268724815</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>0.0187019697445046</v>
+      </c>
+      <c r="Q12" s="0" t="n">
+        <v>4.25853407849128</v>
+      </c>
+      <c r="Y12" s="0" t="n">
+        <v>-77.4</v>
+      </c>
+      <c r="Z12" s="0" t="n">
+        <v>-11.782</v>
+      </c>
+      <c r="AE12" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF12" s="0" t="n">
+        <v>0.0039623627660394</v>
+      </c>
+      <c r="AG12" s="0" t="n">
+        <v>1.1490498112041</v>
+      </c>
+      <c r="AH12" s="0" t="n">
+        <v>0.0257187995074795</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0.0302096076440408</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>0.210027426162091</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>0.244208511148268</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>7.97578375777844</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>4.90910174028173</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <v>0.028294025235832</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <v>17.8051014117079</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <v>372.548856770657</v>
+      </c>
+      <c r="P13" s="0" t="n">
+        <v>0.0035546496374464</v>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <v>49.6695598109063</v>
+      </c>
+      <c r="S13" s="0" t="n">
+        <v>706.989</v>
+      </c>
+      <c r="Y13" s="0" t="n">
+        <v>-72.096</v>
+      </c>
+      <c r="Z13" s="0" t="n">
+        <v>-10.637</v>
+      </c>
+      <c r="AE13" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF13" s="0" t="n">
+        <v>0.0318861255702216</v>
+      </c>
+      <c r="AG13" s="0" t="n">
+        <v>8.16089010264603</v>
+      </c>
+      <c r="AH13" s="0" t="n">
+        <v>0.253532325272266</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>0.0875254301175799</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>0.0588404660565247</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>0.234192078603535</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>7.13615163136324</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <v>4.17159436818663</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <v>0.0374293255227123</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <v>9.2236175997607</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <v>26.4269536398205</v>
+      </c>
+      <c r="P14" s="0" t="n">
+        <v>0.0126979744714284</v>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <v>40.8953117300151</v>
+      </c>
+      <c r="S14" s="0" t="n">
+        <v>46.277</v>
+      </c>
+      <c r="Y14" s="0" t="n">
+        <v>-79.002</v>
+      </c>
+      <c r="Z14" s="0" t="n">
+        <v>-11.277</v>
+      </c>
+      <c r="AE14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF14" s="0" t="n">
+        <v>0.0170906398524396</v>
+      </c>
+      <c r="AG14" s="0" t="n">
+        <v>8.43142560007537</v>
+      </c>
+      <c r="AH14" s="0" t="n">
+        <v>0.199270774511479</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>0.0410559638859827</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>0.345541010312075</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>0.0454222438598574</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>8.05798569874238</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <v>4.16628662716169</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <v>0.0434949232970824</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <v>23.7106117202646</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <v>446.472695181056</v>
+      </c>
+      <c r="P15" s="0" t="n">
+        <v>0.0055377806458749</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>71.1426591625559</v>
+      </c>
+      <c r="S15" s="0" t="n">
+        <v>871.076</v>
+      </c>
+      <c r="Y15" s="0" t="n">
+        <v>-84.283</v>
+      </c>
+      <c r="Z15" s="0" t="n">
+        <v>-12.089</v>
+      </c>
+      <c r="AE15" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF15" s="0" t="n">
+        <v>0.0478915594239327</v>
+      </c>
+      <c r="AG15" s="0" t="n">
+        <v>8.55850597671221</v>
+      </c>
+      <c r="AH15" s="0" t="n">
+        <v>0.320004419536244</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>0.0751811444293779</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>0.066302171333648</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>0.0162875035399794</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>7.14900575892086</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <v>3.3404119502001</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <v>0.0488875367958694</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>9.03838043145902</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <v>27.241451298527</v>
+      </c>
+      <c r="P16" s="0" t="n">
+        <v>0.0084910027358623</v>
+      </c>
+      <c r="Q16" s="0" t="n">
+        <v>43.122176484814</v>
+      </c>
+      <c r="S16" s="0" t="n">
+        <v>44.872</v>
+      </c>
+      <c r="Y16" s="0" t="n">
+        <v>-82.639</v>
+      </c>
+      <c r="Z16" s="0" t="n">
+        <v>-11.809</v>
+      </c>
+      <c r="AE16" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF16" s="0" t="n">
+        <v>0.0188363746139602</v>
+      </c>
+      <c r="AG16" s="0" t="n">
+        <v>8.20691972213249</v>
+      </c>
+      <c r="AH16" s="0" t="n">
+        <v>0.207195348769798</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>0.009092103176771</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>0.0026095486676182</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>0.0041468426920175</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>3.84485177440072</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <v>0.182053032927269</v>
+      </c>
+      <c r="M17" s="0" t="n">
+        <v>0.0197199635885132</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>0.638458896858886</v>
+      </c>
+      <c r="O17" s="0" t="n">
+        <v>0.778910015187182</v>
+      </c>
+      <c r="P17" s="0" t="n">
+        <v>0.0139129260871779</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>4.35130449918243</v>
+      </c>
+      <c r="Y17" s="0" t="n">
+        <v>-89.087</v>
+      </c>
+      <c r="Z17" s="0" t="n">
+        <v>-12.991</v>
+      </c>
+      <c r="AE17" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF17" s="0" t="n">
+        <v>0.0034023637081787</v>
+      </c>
+      <c r="AG17" s="0" t="n">
+        <v>1.21711379744092</v>
+      </c>
+      <c r="AH17" s="0" t="n">
+        <v>0.0267067794038097</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0.0143214772341799</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>0.0022771954467288</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>0.0527793702765137</v>
+      </c>
+      <c r="K18" s="0" t="n">
+        <v>3.18142354274354</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <v>0.232424167727597</v>
+      </c>
+      <c r="M18" s="0" t="n">
+        <v>0.0061969266760085</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <v>0.539838072406454</v>
+      </c>
+      <c r="O18" s="0" t="n">
+        <v>0.689185927757119</v>
+      </c>
+      <c r="P18" s="0" t="n">
+        <v>0.0237250506291488</v>
+      </c>
+      <c r="Q18" s="0" t="n">
+        <v>3.52538032653245</v>
+      </c>
+      <c r="Y18" s="0" t="n">
+        <v>-92.245</v>
+      </c>
+      <c r="Z18" s="0" t="n">
+        <v>-13.659</v>
+      </c>
+      <c r="AE18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF18" s="0" t="n">
+        <v>0.0042576689609612</v>
+      </c>
+      <c r="AG18" s="0" t="n">
+        <v>0.982613097157009</v>
+      </c>
+      <c r="AH18" s="0" t="n">
+        <v>0.0206199409042248</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0.0707585014398432</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>0.0222491754026907</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0.0176956296121753</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <v>5.9094021166089</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <v>2.46520355536095</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>0.0289039370490945</v>
+      </c>
+      <c r="N19" s="0" t="n">
+        <v>6.69177416765634</v>
+      </c>
+      <c r="O19" s="0" t="n">
+        <v>15.7886781306764</v>
+      </c>
+      <c r="P19" s="0" t="n">
+        <v>0.0125072861337549</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>31.9659786759245</v>
+      </c>
+      <c r="S19" s="0" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="Y19" s="0" t="n">
+        <v>-82.382</v>
+      </c>
+      <c r="Z19" s="0" t="n">
+        <v>-11.898</v>
+      </c>
+      <c r="AE19" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF19" s="0" t="n">
+        <v>0.0143519988174014</v>
+      </c>
+      <c r="AG19" s="0" t="n">
+        <v>6.27239148914198</v>
+      </c>
+      <c r="AH19" s="0" t="n">
+        <v>0.154495896206869</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0.040223519908126</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>0.138145730315142</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>0.0062868715789778</v>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>5.93063558890429</v>
+      </c>
+      <c r="L20" s="0" t="n">
+        <v>3.19077377625683</v>
+      </c>
+      <c r="M20" s="0" t="n">
+        <v>0.0313275186188668</v>
+      </c>
+      <c r="N20" s="0" t="n">
+        <v>16.4485849578003</v>
+      </c>
+      <c r="O20" s="0" t="n">
+        <v>225.602905478857</v>
+      </c>
+      <c r="P20" s="0" t="n">
+        <v>0.0118766767467586</v>
+      </c>
+      <c r="Q20" s="0" t="n">
+        <v>44.153575828676</v>
+      </c>
+      <c r="S20" s="0" t="n">
+        <v>419.443</v>
+      </c>
+      <c r="Y20" s="0" t="n">
+        <v>-85.523</v>
+      </c>
+      <c r="Z20" s="0" t="n">
+        <v>-12.244</v>
+      </c>
+      <c r="AE20" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF20" s="0" t="n">
+        <v>0.0297109490064784</v>
+      </c>
+      <c r="AG20" s="0" t="n">
+        <v>6.02051757733667</v>
+      </c>
+      <c r="AH20" s="0" t="n">
+        <v>0.200117214257795</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0.00841292896883</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>0.0020234022367026</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0.0033540315280288</v>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>3.97862414233901</v>
+      </c>
+      <c r="L21" s="0" t="n">
+        <v>0.224145735051009</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>0.004689193560016</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <v>0.6530137109891</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <v>0.768350455883591</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <v>0.0124078399611881</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>4.40342620740259</v>
+      </c>
+      <c r="AE21" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF21" s="0" t="n">
+        <v>0.0038023797782991</v>
+      </c>
+      <c r="AG21" s="0" t="n">
+        <v>1.23729629692767</v>
+      </c>
+      <c r="AH21" s="0" t="n">
+        <v>0.0274065378979662</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="Y22" s="0" t="n">
+        <v>-9.622</v>
+      </c>
+      <c r="Z22" s="0" t="n">
+        <v>-2.618</v>
+      </c>
+      <c r="AE22" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>0.0015683453854584</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>0.0002078923357689</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0.0407648970501766</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>-0.0044309645429649</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <v>0.140769063967067</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>-0.0009534281396155</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>0.0129490201691071</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <v>0.973774901411688</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <v>0.0033868279799188</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <v>0.177868934271168</v>
+      </c>
+      <c r="S23" s="0" t="n">
+        <v>3.535</v>
+      </c>
+      <c r="Y23" s="0" t="n">
+        <v>-150.36</v>
+      </c>
+      <c r="Z23" s="0" t="n">
+        <v>-21.373</v>
+      </c>
+      <c r="AE23" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF23" s="0" t="n">
+        <v>-6.28615798278491E-005</v>
+      </c>
+      <c r="AG23" s="0" t="n">
+        <v>0.0592968715344052</v>
+      </c>
+      <c r="AH23" s="0" t="n">
+        <v>0.0001152657436194</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>0.0036123483417132</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>0.0080939093508421</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>0.427535219809367</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>0.0113744674980154</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>0.274553333050017</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>0.0156683663230229</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>0.0691221846133769</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <v>0.347504942863083</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>0.0093051249969749</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <v>0.469660576142243</v>
+      </c>
+      <c r="S24" s="0" t="n">
+        <v>3.131</v>
+      </c>
+      <c r="Y24" s="0" t="n">
+        <v>-93.003</v>
+      </c>
+      <c r="Z24" s="0" t="n">
+        <v>-13.846</v>
+      </c>
+      <c r="AE24" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF24" s="0" t="n">
+        <v>0.0019774126565885</v>
+      </c>
+      <c r="AG24" s="0" t="n">
+        <v>0.21775324654557</v>
+      </c>
+      <c r="AH24" s="0" t="n">
+        <v>0.001905797267995</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0.0051240279469402</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>0.0027249809211102</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>0.0506362442288233</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>0.0158332366278157</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>0.297722951456968</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>0.0080761144382778</v>
+      </c>
+      <c r="N25" s="0" t="n">
+        <v>0.0674374512182603</v>
+      </c>
+      <c r="O25" s="0" t="n">
+        <v>1.37172775010889</v>
+      </c>
+      <c r="P25" s="0" t="n">
+        <v>0.0065200644292705</v>
+      </c>
+      <c r="Q25" s="0" t="n">
+        <v>0.813715006281711</v>
+      </c>
+      <c r="S25" s="0" t="n">
+        <v>3.871</v>
+      </c>
+      <c r="Y25" s="0" t="n">
+        <v>-167.129</v>
+      </c>
+      <c r="Z25" s="0" t="n">
+        <v>-23.518</v>
+      </c>
+      <c r="AE25" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF25" s="0" t="n">
+        <v>0.0044325021955976</v>
+      </c>
+      <c r="AG25" s="0" t="n">
+        <v>0.196526822616618</v>
+      </c>
+      <c r="AH25" s="0" t="n">
+        <v>0.0016410264902192</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>-0.109</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M26" s="0" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="N26" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="O26" s="0" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="P26" s="0" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="Q26" s="0" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="S26" s="0" t="n">
+        <v>2.054828239</v>
+      </c>
+      <c r="Y26" s="0" t="n">
+        <v>-156.488</v>
+      </c>
+      <c r="Z26" s="0" t="n">
+        <v>-21.724</v>
+      </c>
+      <c r="AE26" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>0.043447278773456</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>0.0144121591045247</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>0.0123448971520179</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>3.50534205814088</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>2.4171964376453</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>0.0186237868065503</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>6.54511825812541</v>
+      </c>
+      <c r="O27" s="0" t="n">
+        <v>13.5730980918428</v>
+      </c>
+      <c r="P27" s="0" t="n">
+        <v>0.0165948456778263</v>
+      </c>
+      <c r="Q27" s="0" t="n">
+        <v>29.69832112582</v>
+      </c>
+      <c r="Y27" s="0" t="n">
+        <v>-93.225</v>
+      </c>
+      <c r="Z27" s="0" t="n">
+        <v>-13.223</v>
+      </c>
+      <c r="AE27" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF27" s="0" t="n">
+        <v>0.0113985944583165</v>
+      </c>
+      <c r="AG27" s="0" t="n">
+        <v>4.7462767603333</v>
+      </c>
+      <c r="AH27" s="0" t="n">
+        <v>0.140988342669605</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>0.0033484007405122</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>0.0056284330562423</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>0.0160707268317587</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>0.467011065768259</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <v>0.215217200596977</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>0.0078441109593032</v>
+      </c>
+      <c r="N28" s="0" t="n">
+        <v>0.424255990289439</v>
+      </c>
+      <c r="O28" s="0" t="n">
+        <v>5.24864115602864</v>
+      </c>
+      <c r="P28" s="0" t="n">
+        <v>0.0024356474910754</v>
+      </c>
+      <c r="Q28" s="0" t="n">
+        <v>2.45004057491752</v>
+      </c>
+      <c r="S28" s="0" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="Y28" s="0" t="n">
+        <v>-152.448</v>
+      </c>
+      <c r="Z28" s="0" t="n">
+        <v>-22.053</v>
+      </c>
+      <c r="AE28" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF28" s="0" t="n">
+        <v>0.0056089310406936</v>
+      </c>
+      <c r="AG28" s="0" t="n">
+        <v>0.450737028629754</v>
+      </c>
+      <c r="AH28" s="0" t="n">
+        <v>0.0062809372500349</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>0.0048310482923197</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>0.0019953586611425</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>0.0168399428814549</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>0.237596332069776</v>
+      </c>
+      <c r="L29" s="0" t="n">
+        <v>0.492079488951174</v>
+      </c>
+      <c r="M29" s="0" t="n">
+        <v>0.0195512771904986</v>
+      </c>
+      <c r="N29" s="0" t="n">
+        <v>0.0775429067471117</v>
+      </c>
+      <c r="O29" s="0" t="n">
+        <v>0.859497027411647</v>
+      </c>
+      <c r="P29" s="0" t="n">
+        <v>0.0034296657767558</v>
+      </c>
+      <c r="Q29" s="0" t="n">
+        <v>0.598009336370448</v>
+      </c>
+      <c r="Y29" s="0" t="n">
+        <v>-155.884</v>
+      </c>
+      <c r="Z29" s="0" t="n">
+        <v>-21.394</v>
+      </c>
+      <c r="AE29" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF29" s="0" t="n">
+        <v>0.0023012455100121</v>
+      </c>
+      <c r="AG29" s="0" t="n">
+        <v>0.118865588602393</v>
+      </c>
+      <c r="AH29" s="0" t="n">
+        <v>0.0012254534111042</v>
+      </c>
+      <c r="AI29" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>0.0090056854259104</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>0.0058330336194845</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>0.0101692750614954</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>0.111223546018091</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <v>0.151347131228407</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <v>0.0048439651206969</v>
+      </c>
+      <c r="N30" s="0" t="n">
+        <v>0.0274486027749156</v>
+      </c>
+      <c r="O30" s="0" t="n">
+        <v>0.127284254568504</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <v>0.0038193952825426</v>
+      </c>
+      <c r="Q30" s="0" t="n">
+        <v>0.163077771836281</v>
+      </c>
+      <c r="Y30" s="0" t="n">
+        <v>-152.074</v>
+      </c>
+      <c r="Z30" s="0" t="n">
+        <v>-21.458</v>
+      </c>
+      <c r="AE30" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF30" s="0" t="n">
+        <v>0.0019525425940387</v>
+      </c>
+      <c r="AG30" s="0" t="n">
+        <v>0.130427970888621</v>
+      </c>
+      <c r="AH30" s="0" t="n">
+        <v>0.0006383426616974</v>
+      </c>
+      <c r="AI30" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>0.0044372934254931</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>0.0017780503523412</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>0.006694135121977</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>0.122360772249421</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>0.538725712614256</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>0.0373200082462041</v>
+      </c>
+      <c r="N31" s="0" t="n">
+        <v>0.0939338318174954</v>
+      </c>
+      <c r="O31" s="0" t="n">
+        <v>0.231900390743295</v>
+      </c>
+      <c r="P31" s="0" t="n">
+        <v>0.0038190989794593</v>
+      </c>
+      <c r="Q31" s="0" t="n">
+        <v>0.391985968776842</v>
+      </c>
+      <c r="Y31" s="0" t="n">
+        <v>-149.428</v>
+      </c>
+      <c r="Z31" s="0" t="n">
+        <v>-20.472</v>
+      </c>
+      <c r="AE31" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF31" s="0" t="n">
+        <v>0.0015355162613786</v>
+      </c>
+      <c r="AG31" s="0" t="n">
+        <v>0.109219412322255</v>
+      </c>
+      <c r="AH31" s="0" t="n">
+        <v>0.0010883024881894</v>
+      </c>
+      <c r="AI31" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>0.0050833171060747</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>0.0190844100867291</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>0.0089514109974359</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>0.155664367719319</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>0.210561964393195</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>-0.0003904801166837</v>
+      </c>
+      <c r="N32" s="0" t="n">
+        <v>0.0434694687978112</v>
+      </c>
+      <c r="O32" s="0" t="n">
+        <v>0.352082325612979</v>
+      </c>
+      <c r="P32" s="0" t="n">
+        <v>0.0035596610760827</v>
+      </c>
+      <c r="Q32" s="0" t="n">
+        <v>0.199072456993824</v>
+      </c>
+      <c r="Y32" s="0" t="n">
+        <v>-140.18</v>
+      </c>
+      <c r="Z32" s="0" t="n">
+        <v>-19.376</v>
+      </c>
+      <c r="AE32" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF32" s="0" t="n">
+        <v>0.0011412160633436</v>
+      </c>
+      <c r="AG32" s="0" t="n">
+        <v>0.0752870954599775</v>
+      </c>
+      <c r="AH32" s="0" t="n">
+        <v>0.0008075152518558</v>
+      </c>
+      <c r="AI32" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>0.0055728464522506</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>0.0029486674679994</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>0.143110948700473</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>1.60541992643776</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>1.10210458718038</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>0.0161624150683374</v>
+      </c>
+      <c r="N33" s="0" t="n">
+        <v>2.0553962205514</v>
+      </c>
+      <c r="O33" s="0" t="n">
+        <v>2.11030481776085</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>0.0093401889249047</v>
+      </c>
+      <c r="Q33" s="0" t="n">
+        <v>6.4216020367105</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>2.958</v>
+      </c>
+      <c r="Y33" s="0" t="n">
+        <v>-123.17</v>
+      </c>
+      <c r="Z33" s="0" t="n">
+        <v>-17.298</v>
+      </c>
+      <c r="AE33" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF33" s="0" t="n">
+        <v>0.0026757259571924</v>
+      </c>
+      <c r="AG33" s="0" t="n">
+        <v>0.366351292220491</v>
+      </c>
+      <c r="AH33" s="0" t="n">
+        <v>0.0288768722897383</v>
+      </c>
+      <c r="AI33" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>0.0061298493596715</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>0.0016552155918288</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>0.150548781570325</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>1.4172924153914</v>
+      </c>
+      <c r="L34" s="0" t="n">
+        <v>1.70404439561823</v>
+      </c>
+      <c r="M34" s="0" t="n">
+        <v>0.0339328508209458</v>
+      </c>
+      <c r="N34" s="0" t="n">
+        <v>2.35433564653784</v>
+      </c>
+      <c r="O34" s="0" t="n">
+        <v>11.812029731631</v>
+      </c>
+      <c r="P34" s="0" t="n">
+        <v>0.0096198242074704</v>
+      </c>
+      <c r="Q34" s="0" t="n">
+        <v>4.70277981917326</v>
+      </c>
+      <c r="S34" s="0" t="n">
+        <v>4.043</v>
+      </c>
+      <c r="Y34" s="0" t="n">
+        <v>-123.809</v>
+      </c>
+      <c r="Z34" s="0" t="n">
+        <v>-17.231</v>
+      </c>
+      <c r="AE34" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF34" s="0" t="n">
+        <v>0.0029491797109797</v>
+      </c>
+      <c r="AG34" s="0" t="n">
+        <v>0.312199161807893</v>
+      </c>
+      <c r="AH34" s="0" t="n">
+        <v>0.0257779149491529</v>
+      </c>
+      <c r="AI34" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>0.0110533640451155</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>0.0077234344973359</v>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>0.214752077607589</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>2.93561810180913</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <v>3.82262123793148</v>
+      </c>
+      <c r="M35" s="0" t="n">
+        <v>0.0572067676038611</v>
+      </c>
+      <c r="N35" s="0" t="n">
+        <v>10.9752974071741</v>
+      </c>
+      <c r="O35" s="0" t="n">
+        <v>8.3939332885478</v>
+      </c>
+      <c r="P35" s="0" t="n">
+        <v>0.009286321725069</v>
+      </c>
+      <c r="Q35" s="0" t="n">
+        <v>10.5272144987431</v>
+      </c>
+      <c r="S35" s="0" t="n">
+        <v>6.392</v>
+      </c>
+      <c r="Y35" s="0" t="n">
+        <v>-86.159</v>
+      </c>
+      <c r="Z35" s="0" t="n">
+        <v>-12.902</v>
+      </c>
+      <c r="AE35" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF35" s="0" t="n">
+        <v>0.0071948680930558</v>
+      </c>
+      <c r="AG35" s="0" t="n">
+        <v>0.819163953291818</v>
+      </c>
+      <c r="AH35" s="0" t="n">
+        <v>0.0756159820645211</v>
+      </c>
+      <c r="AI35" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="N36" s="0" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="O36" s="0" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="P36" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q36" s="0" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S36" s="0" t="n">
+        <v>5.298</v>
+      </c>
+      <c r="Y36" s="0" t="n">
+        <v>-130.899</v>
+      </c>
+      <c r="Z36" s="0" t="n">
+        <v>-18.526</v>
+      </c>
+      <c r="AE36" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI36" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="M37" s="0" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N37" s="0" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="O37" s="0" t="n">
+        <v>0.814</v>
+      </c>
+      <c r="P37" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Q37" s="0" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="S37" s="0" t="n">
+        <v>2.613238111</v>
+      </c>
+      <c r="Y37" s="0" t="n">
+        <v>-121.24</v>
+      </c>
+      <c r="Z37" s="0" t="n">
+        <v>-17.13</v>
+      </c>
+      <c r="AE37" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI37" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="M38" s="0" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="N38" s="0" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O38" s="0" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="P38" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q38" s="0" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="S38" s="0" t="n">
+        <v>1.664083231</v>
+      </c>
+      <c r="Y38" s="0" t="n">
+        <v>-123.895</v>
+      </c>
+      <c r="Z38" s="0" t="n">
+        <v>-17.346</v>
+      </c>
+      <c r="AE38" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI38" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K39" s="0" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="L39" s="0" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N39" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O39" s="0" t="n">
+        <v>5.252</v>
+      </c>
+      <c r="P39" s="0" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="Q39" s="0" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="S39" s="0" t="n">
+        <v>3.640859084</v>
+      </c>
+      <c r="Y39" s="0" t="n">
+        <v>-146.128</v>
+      </c>
+      <c r="Z39" s="0" t="n">
+        <v>-18.863</v>
+      </c>
+      <c r="AE39" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI39" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L40" s="0" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="O40" s="0" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="P40" s="0" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="Q40" s="0" t="n">
+        <v>2.368</v>
+      </c>
+      <c r="S40" s="0" t="n">
+        <v>4.19693782</v>
+      </c>
+      <c r="Y40" s="0" t="n">
+        <v>-96.514</v>
+      </c>
+      <c r="Z40" s="0" t="n">
+        <v>-13.525</v>
+      </c>
+      <c r="AE40" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI40" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="L41" s="0" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="N41" s="0" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="O41" s="0" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="P41" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q41" s="0" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="S41" s="0" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="Y41" s="0" t="n">
+        <v>-158.817</v>
+      </c>
+      <c r="Z41" s="0" t="n">
+        <v>-21.928</v>
+      </c>
+      <c r="AE41" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI41" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="L42" s="0" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="N42" s="0" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="O42" s="0" t="n">
+        <v>6.062</v>
+      </c>
+      <c r="P42" s="0" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="Q42" s="0" t="n">
+        <v>6.236</v>
+      </c>
+      <c r="S42" s="0" t="n">
+        <v>4.209</v>
+      </c>
+      <c r="Y42" s="0" t="n">
+        <v>-142.804</v>
+      </c>
+      <c r="Z42" s="0" t="n">
+        <v>-19.249</v>
+      </c>
+      <c r="AE42" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI42" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K43" s="0" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L43" s="0" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="N43" s="0" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="O43" s="0" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="P43" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q43" s="0" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="S43" s="0" t="n">
+        <v>3.699</v>
+      </c>
+      <c r="Y43" s="0" t="n">
+        <v>-134.317</v>
+      </c>
+      <c r="Z43" s="0" t="n">
+        <v>-18.463</v>
+      </c>
+      <c r="AE43" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI43" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="L44" s="0" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="N44" s="0" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="O44" s="0" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="P44" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q44" s="0" t="n">
+        <v>2.698</v>
+      </c>
+      <c r="S44" s="0" t="n">
+        <v>3.154</v>
+      </c>
+      <c r="Y44" s="0" t="n">
+        <v>-92.57</v>
+      </c>
+      <c r="Z44" s="0" t="n">
+        <v>-13.192</v>
+      </c>
+      <c r="AE44" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI44" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>0.0085346094474101</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>0.0018054059988524</v>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>0.0164660508676089</v>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>1.61513276249999</v>
+      </c>
+      <c r="L45" s="0" t="n">
+        <v>0.555337896010912</v>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>0.0589185094617445</v>
+      </c>
+      <c r="N45" s="0" t="n">
+        <v>0.672854084978792</v>
+      </c>
+      <c r="O45" s="0" t="n">
+        <v>2.79161428014061</v>
+      </c>
+      <c r="P45" s="0" t="n">
+        <v>0.0084426448757301</v>
+      </c>
+      <c r="Q45" s="0" t="n">
+        <v>2.08239530002949</v>
+      </c>
+      <c r="Y45" s="0" t="n">
+        <v>-127.762</v>
+      </c>
+      <c r="Z45" s="0" t="n">
+        <v>-17.778</v>
+      </c>
+      <c r="AE45" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF45" s="0" t="n">
+        <v>0.0016379279445865</v>
+      </c>
+      <c r="AG45" s="0" t="n">
+        <v>0.319000171215353</v>
+      </c>
+      <c r="AH45" s="0" t="n">
+        <v>0.010086773231093</v>
+      </c>
+      <c r="AI45" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>0.0227123197248299</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>0.0115599926884761</v>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>0.0388084230920984</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>5.79073167133884</v>
+      </c>
+      <c r="L46" s="0" t="n">
+        <v>1.51046674993606</v>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>0.35263866327542</v>
+      </c>
+      <c r="N46" s="0" t="n">
+        <v>3.00894347882435</v>
+      </c>
+      <c r="O46" s="0" t="n">
+        <v>12.6357123601275</v>
+      </c>
+      <c r="P46" s="0" t="n">
+        <v>0.0512764698798423</v>
+      </c>
+      <c r="Q46" s="0" t="n">
+        <v>5.76867796640229</v>
+      </c>
+      <c r="S46" s="0" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="Y46" s="0" t="n">
+        <v>-132.014</v>
+      </c>
+      <c r="Z46" s="0" t="n">
+        <v>-18.18</v>
+      </c>
+      <c r="AE46" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF46" s="0" t="n">
+        <v>0.0050567207324497</v>
+      </c>
+      <c r="AG46" s="0" t="n">
+        <v>1.19393749814484</v>
+      </c>
+      <c r="AH46" s="0" t="n">
+        <v>0.0310008930696641</v>
+      </c>
+      <c r="AI46" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>0.0019760942116579</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>0.0050026388525218</v>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>0.0527958007589164</v>
+      </c>
+      <c r="K47" s="0" t="n">
+        <v>0.812398171475216</v>
+      </c>
+      <c r="L47" s="0" t="n">
+        <v>0.543924483790156</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>0.0904386350627342</v>
+      </c>
+      <c r="N47" s="0" t="n">
+        <v>0.705251076812835</v>
+      </c>
+      <c r="O47" s="0" t="n">
+        <v>10.3653520428217</v>
+      </c>
+      <c r="P47" s="0" t="n">
+        <v>0.0025749852686756</v>
+      </c>
+      <c r="Q47" s="0" t="n">
+        <v>2.14314368066845</v>
+      </c>
+      <c r="S47" s="0" t="n">
+        <v>7.758</v>
+      </c>
+      <c r="Y47" s="0" t="n">
+        <v>-110.149</v>
+      </c>
+      <c r="Z47" s="0" t="n">
+        <v>-15.173</v>
+      </c>
+      <c r="AE47" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF47" s="0" t="n">
+        <v>0.0004060160156863</v>
+      </c>
+      <c r="AG47" s="0" t="n">
+        <v>0.323447062157401</v>
+      </c>
+      <c r="AH47" s="0" t="n">
+        <v>0.0081862627609175</v>
+      </c>
+      <c r="AI47" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>0.003306156052009</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>0.0052858641309003</v>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>0.007167393122649</v>
+      </c>
+      <c r="K48" s="0" t="n">
+        <v>1.14221824890617</v>
+      </c>
+      <c r="L48" s="0" t="n">
+        <v>0.29920542380775</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>0.0481668231898921</v>
+      </c>
+      <c r="N48" s="0" t="n">
+        <v>0.679363463978907</v>
+      </c>
+      <c r="O48" s="0" t="n">
+        <v>2.72599185143812</v>
+      </c>
+      <c r="P48" s="0" t="n">
+        <v>0.0022513617721481</v>
+      </c>
+      <c r="Q48" s="0" t="n">
+        <v>1.88573587045601</v>
+      </c>
+      <c r="S48" s="0" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="Y48" s="0" t="n">
+        <v>-97.252</v>
+      </c>
+      <c r="Z48" s="0" t="n">
+        <v>-13.486</v>
+      </c>
+      <c r="AE48" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF48" s="0" t="n">
+        <v>0.0009122156802799</v>
+      </c>
+      <c r="AG48" s="0" t="n">
+        <v>0.182541757523821</v>
+      </c>
+      <c r="AH48" s="0" t="n">
+        <v>0.0074560326980783</v>
+      </c>
+      <c r="AI48" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>0.0098635310971857</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>0.0140500260465246</v>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>0.0509245017605753</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>0.1981908582859</v>
+      </c>
+      <c r="L49" s="0" t="n">
+        <v>0.594047623044881</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>0.0120155874002578</v>
+      </c>
+      <c r="N49" s="0" t="n">
+        <v>0.294648750317538</v>
+      </c>
+      <c r="O49" s="0" t="n">
+        <v>0.906987291608009</v>
+      </c>
+      <c r="P49" s="0" t="n">
+        <v>0.018329827298502</v>
+      </c>
+      <c r="Q49" s="0" t="n">
+        <v>1.05126461350751</v>
+      </c>
+      <c r="Y49" s="0" t="n">
+        <v>-161.961</v>
+      </c>
+      <c r="Z49" s="0" t="n">
+        <v>-22.037</v>
+      </c>
+      <c r="AE49" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF49" s="0" t="n">
+        <v>0.0008554067434984</v>
+      </c>
+      <c r="AG49" s="0" t="n">
+        <v>0.300303855810626</v>
+      </c>
+      <c r="AH49" s="0" t="n">
+        <v>0.0055840668126927</v>
+      </c>
+      <c r="AI49" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>0.0106527241176964</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>0.0100103480278188</v>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>0.0269275473725334</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>0.186822453494061</v>
+      </c>
+      <c r="L50" s="0" t="n">
+        <v>0.750696603622076</v>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>0.0344458136771672</v>
+      </c>
+      <c r="N50" s="0" t="n">
+        <v>0.277737044107506</v>
+      </c>
+      <c r="O50" s="0" t="n">
+        <v>0.723701940358386</v>
+      </c>
+      <c r="P50" s="0" t="n">
+        <v>0.0121497666038943</v>
+      </c>
+      <c r="Q50" s="0" t="n">
+        <v>1.1216511729118</v>
+      </c>
+      <c r="S50" s="0" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="Y50" s="0" t="n">
+        <v>-112.538</v>
+      </c>
+      <c r="Z50" s="0" t="n">
+        <v>-15.487</v>
+      </c>
+      <c r="AE50" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF50" s="0" t="n">
+        <v>0.0023457894441581</v>
+      </c>
+      <c r="AG50" s="0" t="n">
+        <v>0.137375946609836</v>
+      </c>
+      <c r="AH50" s="0" t="n">
+        <v>0.0049807538078414</v>
+      </c>
+      <c r="AI50" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>0.0074244643645789</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>0.0091086709624915</v>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>0.0165948878584498</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>0.173011848006445</v>
+      </c>
+      <c r="L51" s="0" t="n">
+        <v>0.487547030439495</v>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>0.0145816444168773</v>
+      </c>
+      <c r="N51" s="0" t="n">
+        <v>0.116653337932215</v>
+      </c>
+      <c r="O51" s="0" t="n">
+        <v>0.337633722564304</v>
+      </c>
+      <c r="P51" s="0" t="n">
+        <v>0.0071169169761825</v>
+      </c>
+      <c r="Q51" s="0" t="n">
+        <v>0.405398585281557</v>
+      </c>
+      <c r="Y51" s="0" t="n">
+        <v>-144.825</v>
+      </c>
+      <c r="Z51" s="0" t="n">
+        <v>-19.965</v>
+      </c>
+      <c r="AE51" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF51" s="0" t="n">
+        <v>0.0008547011946214</v>
+      </c>
+      <c r="AG51" s="0" t="n">
+        <v>0.141262966888262</v>
+      </c>
+      <c r="AH51" s="0" t="n">
+        <v>0.0023225113028545</v>
+      </c>
+      <c r="AI51" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>0.0144955578055677</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>0.0071920655388572</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>0.0038817867105999</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>0.368928661744995</v>
+      </c>
+      <c r="L52" s="0" t="n">
+        <v>0.755043635361557</v>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>0.023840136837084</v>
+      </c>
+      <c r="N52" s="0" t="n">
+        <v>0.468033026260817</v>
+      </c>
+      <c r="O52" s="0" t="n">
+        <v>0.924824089584703</v>
+      </c>
+      <c r="P52" s="0" t="n">
+        <v>0.0169517455685153</v>
+      </c>
+      <c r="Q52" s="0" t="n">
+        <v>1.27565818036987</v>
+      </c>
+      <c r="S52" s="0" t="n">
+        <v>1.872</v>
+      </c>
+      <c r="Y52" s="0" t="n">
+        <v>-116.792</v>
+      </c>
+      <c r="Z52" s="0" t="n">
+        <v>-15.922</v>
+      </c>
+      <c r="AE52" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF52" s="0" t="n">
+        <v>0.0022844961057745</v>
+      </c>
+      <c r="AG52" s="0" t="n">
+        <v>0.081996201329727</v>
+      </c>
+      <c r="AH52" s="0" t="n">
+        <v>0.0072821840187373</v>
+      </c>
+      <c r="AI52" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>0.0057769133357339</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>0.0035080847051434</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>0.0076269883562921</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>1.65398643420911</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <v>0.58941927607672</v>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>0.0228083866500874</v>
+      </c>
+      <c r="N53" s="0" t="n">
+        <v>0.640358534165793</v>
+      </c>
+      <c r="O53" s="0" t="n">
+        <v>2.11162396780117</v>
+      </c>
+      <c r="P53" s="0" t="n">
+        <v>0.0037598151844479</v>
+      </c>
+      <c r="Q53" s="0" t="n">
+        <v>1.94346669704879</v>
+      </c>
+      <c r="S53" s="0" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="Y53" s="0" t="n">
+        <v>-82.365</v>
+      </c>
+      <c r="Z53" s="0" t="n">
+        <v>-10.962</v>
+      </c>
+      <c r="AE53" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF53" s="0" t="n">
+        <v>0.0008944476819299</v>
+      </c>
+      <c r="AG53" s="0" t="n">
+        <v>0.18069603184567</v>
+      </c>
+      <c r="AH53" s="0" t="n">
+        <v>0.0099982970183845</v>
+      </c>
+      <c r="AI53" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>0.0050293764244089</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>0.0113563035296846</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>0.0805626222238855</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>0.295138241664404</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>0.812808715495903</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>0.0093352459503896</v>
+      </c>
+      <c r="N54" s="0" t="n">
+        <v>0.133976670078496</v>
+      </c>
+      <c r="O54" s="0" t="n">
+        <v>0.462552906224064</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>0.0249026085075288</v>
+      </c>
+      <c r="Q54" s="0" t="n">
+        <v>0.489042125094086</v>
+      </c>
+      <c r="Y54" s="0" t="n">
+        <v>-113.637</v>
+      </c>
+      <c r="Z54" s="0" t="n">
+        <v>-15.855</v>
+      </c>
+      <c r="AE54" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF54" s="0" t="n">
+        <v>0.0010773422919634</v>
+      </c>
+      <c r="AG54" s="0" t="n">
+        <v>0.163327994264156</v>
+      </c>
+      <c r="AH54" s="0" t="n">
+        <v>0.0028466662088906</v>
+      </c>
+      <c r="AI54" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>0.0074147920842676</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>0.0051941881983693</v>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>0.0868963134996833</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>0.562828779261674</v>
+      </c>
+      <c r="L55" s="0" t="n">
+        <v>0.576386244088574</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>0.0075926176319185</v>
+      </c>
+      <c r="N55" s="0" t="n">
+        <v>0.125219376272607</v>
+      </c>
+      <c r="O55" s="0" t="n">
+        <v>0.278794139651271</v>
+      </c>
+      <c r="P55" s="0" t="n">
+        <v>0.0311498138740462</v>
+      </c>
+      <c r="Q55" s="0" t="n">
+        <v>0.426163773040128</v>
+      </c>
+      <c r="Y55" s="0" t="n">
+        <v>-84.147</v>
+      </c>
+      <c r="Z55" s="0" t="n">
+        <v>-11.896</v>
+      </c>
+      <c r="AE55" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF55" s="0" t="n">
+        <v>0.0013233458615952</v>
+      </c>
+      <c r="AG55" s="0" t="n">
+        <v>0.14814875974295</v>
+      </c>
+      <c r="AH55" s="0" t="n">
+        <v>0.0025705355171308</v>
+      </c>
+      <c r="AI55" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>0.216255741046689</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>0.0100404181948112</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>0.443365587890954</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>1.06242959457586</v>
+      </c>
+      <c r="L56" s="0" t="n">
+        <v>0.278540049787593</v>
+      </c>
+      <c r="M56" s="0" t="n">
+        <v>0.007031472337809</v>
+      </c>
+      <c r="N56" s="0" t="n">
+        <v>0.310526288452836</v>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>0.361980813179073</v>
+      </c>
+      <c r="P56" s="0" t="n">
+        <v>0.736171147470417</v>
+      </c>
+      <c r="Q56" s="0" t="n">
+        <v>0.858941566800132</v>
+      </c>
+      <c r="S56" s="0" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="Y56" s="0" t="n">
+        <v>-100.162</v>
+      </c>
+      <c r="Z56" s="0" t="n">
+        <v>-14.696</v>
+      </c>
+      <c r="AE56" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF56" s="0" t="n">
+        <v>0.0090682491491102</v>
+      </c>
+      <c r="AG56" s="0" t="n">
+        <v>0.682493684399541</v>
+      </c>
+      <c r="AH56" s="0" t="n">
+        <v>0.0060975957285925</v>
+      </c>
+      <c r="AI56" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="L57" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M57" s="0" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O57" s="0" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="P57" s="0" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="Q57" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S57" s="0" t="n">
+        <v>3.123</v>
+      </c>
+      <c r="Y57" s="0" t="n">
+        <v>-108.5</v>
+      </c>
+      <c r="Z57" s="0" t="n">
+        <v>-15.623</v>
+      </c>
+      <c r="AE57" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI57" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="L58" s="0" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="M58" s="0" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="N58" s="0" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="Q58" s="0" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Y58" s="0" t="n">
+        <v>-121.868</v>
+      </c>
+      <c r="Z58" s="0" t="n">
+        <v>-17.072</v>
+      </c>
+      <c r="AE58" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI58" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>5.204</v>
+      </c>
+      <c r="L59" s="0" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="M59" s="0" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="N59" s="0" t="n">
+        <v>3.982</v>
+      </c>
+      <c r="O59" s="0" t="n">
+        <v>6.927</v>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="Q59" s="0" t="n">
+        <v>28.675</v>
+      </c>
+      <c r="S59" s="0" t="n">
+        <v>14.876</v>
+      </c>
+      <c r="Y59" s="0" t="n">
+        <v>-83.179</v>
+      </c>
+      <c r="Z59" s="0" t="n">
+        <v>-12.068</v>
+      </c>
+      <c r="AE59" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI59" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>0.0961438679861533</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>0.0016515970368478</v>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>0.017911759130375</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>2.69107565167914</v>
+      </c>
+      <c r="L60" s="0" t="n">
+        <v>0.124891453142565</v>
+      </c>
+      <c r="M60" s="0" t="n">
+        <v>0.009742624874038</v>
+      </c>
+      <c r="N60" s="0" t="n">
+        <v>0.117381357762017</v>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>0.127532164929982</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>0.34351025154112</v>
+      </c>
+      <c r="Q60" s="0" t="n">
+        <v>0.311310064011197</v>
+      </c>
+      <c r="Y60" s="0" t="n">
+        <v>-81.293</v>
+      </c>
+      <c r="Z60" s="0" t="n">
+        <v>-12.148</v>
+      </c>
+      <c r="AE60" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF60" s="0" t="n">
+        <v>0.0042461749510821</v>
+      </c>
+      <c r="AG60" s="0" t="n">
+        <v>0.196826480405888</v>
+      </c>
+      <c r="AH60" s="0" t="n">
+        <v>0.0024868839629022</v>
+      </c>
+      <c r="AI60" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>0.0257509398792981</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>0.0012978641894512</v>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>0.0134657431547053</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>14.5822070208133</v>
+      </c>
+      <c r="L61" s="0" t="n">
+        <v>0.528292767436512</v>
+      </c>
+      <c r="M61" s="0" t="n">
+        <v>0.0951889752521298</v>
+      </c>
+      <c r="N61" s="0" t="n">
+        <v>4.97139774042044</v>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>7.57597930699061</v>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>0.0354620646286075</v>
+      </c>
+      <c r="Q61" s="0" t="n">
+        <v>37.3338544826754</v>
+      </c>
+      <c r="S61" s="0" t="n">
+        <v>12.588</v>
+      </c>
+      <c r="Y61" s="0" t="n">
+        <v>-63.812</v>
+      </c>
+      <c r="Z61" s="0" t="n">
+        <v>-9.538</v>
+      </c>
+      <c r="AE61" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF61" s="0" t="n">
+        <v>0.0237414790824847</v>
+      </c>
+      <c r="AG61" s="0" t="n">
+        <v>15.696387208996</v>
+      </c>
+      <c r="AH61" s="0" t="n">
+        <v>0.150206218490675</v>
+      </c>
+      <c r="AI61" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y62" s="0" t="n">
+        <v>-55.86</v>
+      </c>
+      <c r="Z62" s="0" t="n">
+        <v>-8.628</v>
+      </c>
+      <c r="AE62" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI62" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>0.0942685608067847</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>0.0029730914136302</v>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>0.902381504079543</v>
+      </c>
+      <c r="K63" s="0" t="n">
+        <v>2.37217692140535</v>
+      </c>
+      <c r="L63" s="0" t="n">
+        <v>0.400441140326505</v>
+      </c>
+      <c r="M63" s="0" t="n">
+        <v>0.0105717148314338</v>
+      </c>
+      <c r="N63" s="0" t="n">
+        <v>0.114725286867467</v>
+      </c>
+      <c r="O63" s="0" t="n">
+        <v>0.201120747249083</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>0.302230173900663</v>
+      </c>
+      <c r="Q63" s="0" t="n">
+        <v>0.482012395003098</v>
+      </c>
+      <c r="Y63" s="0" t="n">
+        <v>-76.484</v>
+      </c>
+      <c r="Z63" s="0" t="n">
+        <v>-11.243</v>
+      </c>
+      <c r="AE63" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF63" s="0" t="n">
+        <v>0.005087494871497</v>
+      </c>
+      <c r="AG63" s="0" t="n">
+        <v>0.230593321458091</v>
+      </c>
+      <c r="AH63" s="0" t="n">
+        <v>0.0026058777304597</v>
+      </c>
+      <c r="AI63" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>0.0185475320278764</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>0.0022797603268471</v>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>0.0298922816318826</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>14.8139957762255</v>
+      </c>
+      <c r="L64" s="0" t="n">
+        <v>0.680912078855531</v>
+      </c>
+      <c r="M64" s="0" t="n">
+        <v>0.0584645100820437</v>
+      </c>
+      <c r="N64" s="0" t="n">
+        <v>4.96384853356119</v>
+      </c>
+      <c r="O64" s="0" t="n">
+        <v>7.18588163926732</v>
+      </c>
+      <c r="P64" s="0" t="n">
+        <v>0.0236952447995943</v>
+      </c>
+      <c r="Q64" s="0" t="n">
+        <v>37.4072599917519</v>
+      </c>
+      <c r="S64" s="0" t="n">
+        <v>13.863</v>
+      </c>
+      <c r="Y64" s="0" t="n">
+        <v>-63.046</v>
+      </c>
+      <c r="Z64" s="0" t="n">
+        <v>-9.42</v>
+      </c>
+      <c r="AE64" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF64" s="0" t="n">
+        <v>0.0237286878617453</v>
+      </c>
+      <c r="AG64" s="0" t="n">
+        <v>15.7769320818403</v>
+      </c>
+      <c r="AH64" s="0" t="n">
+        <v>0.151496211928396</v>
+      </c>
+      <c r="AI64" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>0.0987472072965153</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>0.0148500470985387</v>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>0.0598189309859664</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>4.80781440303856</v>
+      </c>
+      <c r="L65" s="0" t="n">
+        <v>9.55718890005296</v>
+      </c>
+      <c r="M65" s="0" t="n">
+        <v>1.40358265684637</v>
+      </c>
+      <c r="N65" s="0" t="n">
+        <v>2.61499526690342</v>
+      </c>
+      <c r="O65" s="0" t="n">
+        <v>0.452485822021034</v>
+      </c>
+      <c r="P65" s="0" t="n">
+        <v>0.107948966158962</v>
+      </c>
+      <c r="Q65" s="0" t="n">
+        <v>13.0712436822085</v>
+      </c>
+      <c r="S65" s="0" t="n">
+        <v>4.895</v>
+      </c>
+      <c r="Y65" s="0" t="n">
+        <v>-96.976</v>
+      </c>
+      <c r="Z65" s="0" t="n">
+        <v>-14.06</v>
+      </c>
+      <c r="AE65" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF65" s="0" t="n">
+        <v>0.0081829252014912</v>
+      </c>
+      <c r="AG65" s="0" t="n">
+        <v>1.06303871011562</v>
+      </c>
+      <c r="AH65" s="0" t="n">
+        <v>0.0300979487763582</v>
+      </c>
+      <c r="AI65" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>0.0213735545121297</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>0.0037683450350384</v>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>0.230574939764419</v>
+      </c>
+      <c r="K66" s="0" t="n">
+        <v>0.695155027837233</v>
+      </c>
+      <c r="L66" s="0" t="n">
+        <v>9.44596948773602</v>
+      </c>
+      <c r="M66" s="0" t="n">
+        <v>0.516221778479183</v>
+      </c>
+      <c r="N66" s="0" t="n">
+        <v>1.20607330720948</v>
+      </c>
+      <c r="O66" s="0" t="n">
+        <v>3.89027238814901</v>
+      </c>
+      <c r="P66" s="0" t="n">
+        <v>0.020419926475139</v>
+      </c>
+      <c r="Q66" s="0" t="n">
+        <v>4.98714756177296</v>
+      </c>
+      <c r="S66" s="0" t="n">
+        <v>6.847</v>
+      </c>
+      <c r="Y66" s="0" t="n">
+        <v>-107.579</v>
+      </c>
+      <c r="Z66" s="0" t="n">
+        <v>-14.984</v>
+      </c>
+      <c r="AE66" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF66" s="0" t="n">
+        <v>0.0044332393434243</v>
+      </c>
+      <c r="AG66" s="0" t="n">
+        <v>0.579027796674627</v>
+      </c>
+      <c r="AH66" s="0" t="n">
+        <v>0.0140370688651896</v>
+      </c>
+      <c r="AI66" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F67" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <v>0.0263091477739987</v>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>0.0010961804297588</v>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>0.0172401564022104</v>
+      </c>
+      <c r="K67" s="0" t="n">
+        <v>0.536106316371191</v>
+      </c>
+      <c r="L67" s="0" t="n">
+        <v>6.24344686158433</v>
+      </c>
+      <c r="M67" s="0" t="n">
+        <v>0.359538157366964</v>
+      </c>
+      <c r="N67" s="0" t="n">
+        <v>1.22193633386238</v>
+      </c>
+      <c r="O67" s="0" t="n">
+        <v>2.70910237928903</v>
+      </c>
+      <c r="P67" s="0" t="n">
+        <v>0.0196330946261334</v>
+      </c>
+      <c r="Q67" s="0" t="n">
+        <v>4.70371684514793</v>
+      </c>
+      <c r="S67" s="0" t="n">
+        <v>5.002</v>
+      </c>
+      <c r="Y67" s="0" t="n">
+        <v>-104.657</v>
+      </c>
+      <c r="Z67" s="0" t="n">
+        <v>-14.507</v>
+      </c>
+      <c r="AE67" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF67" s="0" t="n">
+        <v>0.0048666176943241</v>
+      </c>
+      <c r="AG67" s="0" t="n">
+        <v>0.440284955614656</v>
+      </c>
+      <c r="AH67" s="0" t="n">
+        <v>0.0137741117522103</v>
+      </c>
+      <c r="AI67" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>0.0196978101604263</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>0.0030695363116819</v>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>0.0075680450258891</v>
+      </c>
+      <c r="K68" s="0" t="n">
+        <v>14.2149798291812</v>
+      </c>
+      <c r="L68" s="0" t="n">
+        <v>0.260458420965447</v>
+      </c>
+      <c r="M68" s="0" t="n">
+        <v>0.0891658278457207</v>
+      </c>
+      <c r="N68" s="0" t="n">
+        <v>5.19866547645978</v>
+      </c>
+      <c r="O68" s="0" t="n">
+        <v>7.4256838671046</v>
+      </c>
+      <c r="P68" s="0" t="n">
+        <v>0.0206062939539302</v>
+      </c>
+      <c r="Q68" s="0" t="n">
+        <v>37.3534551404776</v>
+      </c>
+      <c r="S68" s="0" t="n">
+        <v>11.373</v>
+      </c>
+      <c r="Y68" s="0" t="n">
+        <v>-69.765</v>
+      </c>
+      <c r="Z68" s="0" t="n">
+        <v>-10.385</v>
+      </c>
+      <c r="AE68" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF68" s="0" t="n">
+        <v>0.0206602268282388</v>
+      </c>
+      <c r="AG68" s="0" t="n">
+        <v>11.6386971004496</v>
+      </c>
+      <c r="AH68" s="0" t="n">
+        <v>0.147434582450313</v>
+      </c>
+      <c r="AI68" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>0.101765238034797</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>0.0018966321689301</v>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>0.0751039715822787</v>
+      </c>
+      <c r="K69" s="0" t="n">
+        <v>2.40766324470149</v>
+      </c>
+      <c r="L69" s="0" t="n">
+        <v>0.379094900792271</v>
+      </c>
+      <c r="M69" s="0" t="n">
+        <v>0.0087073367186248</v>
+      </c>
+      <c r="N69" s="0" t="n">
+        <v>0.137331118412547</v>
+      </c>
+      <c r="O69" s="0" t="n">
+        <v>0.270041434547446</v>
+      </c>
+      <c r="P69" s="0" t="n">
+        <v>0.366951883474271</v>
+      </c>
+      <c r="Q69" s="0" t="n">
+        <v>0.293645560855869</v>
+      </c>
+      <c r="Y69" s="0" t="n">
+        <v>-113.574</v>
+      </c>
+      <c r="Z69" s="0" t="n">
+        <v>-16.037</v>
+      </c>
+      <c r="AE69" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF69" s="0" t="n">
+        <v>0.0046436344154738</v>
+      </c>
+      <c r="AG69" s="0" t="n">
+        <v>0.328974064642618</v>
+      </c>
+      <c r="AH69" s="0" t="n">
+        <v>0.0025641808304098</v>
+      </c>
+      <c r="AI69" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>0.0541854801088563</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>0.0122652189596925</v>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>0.116163639862738</v>
+      </c>
+      <c r="K70" s="0" t="n">
+        <v>1.27161193295264</v>
+      </c>
+      <c r="L70" s="0" t="n">
+        <v>0.572828264720966</v>
+      </c>
+      <c r="M70" s="0" t="n">
+        <v>0.0277393435542943</v>
+      </c>
+      <c r="N70" s="0" t="n">
+        <v>0.2685030063957</v>
+      </c>
+      <c r="O70" s="0" t="n">
+        <v>0.356769166134891</v>
+      </c>
+      <c r="P70" s="0" t="n">
+        <v>0.456166801535497</v>
+      </c>
+      <c r="Q70" s="0" t="n">
+        <v>1.49180709707671</v>
+      </c>
+      <c r="S70" s="0" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="Y70" s="0" t="n">
+        <v>-60.017</v>
+      </c>
+      <c r="Z70" s="0" t="n">
+        <v>-9.172</v>
+      </c>
+      <c r="AE70" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF70" s="0" t="n">
+        <v>0.0110697588532729</v>
+      </c>
+      <c r="AG70" s="0" t="n">
+        <v>0.81234649316421</v>
+      </c>
+      <c r="AH70" s="0" t="n">
+        <v>0.0133558954313582</v>
+      </c>
+      <c r="AI70" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="S71" s="0" t="n">
+        <v>5.064</v>
+      </c>
+      <c r="Y71" s="0" t="n">
+        <v>-62.853</v>
+      </c>
+      <c r="Z71" s="0" t="n">
+        <v>-9.877</v>
+      </c>
+      <c r="AE71" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI71" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F72" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K72" s="0" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="L72" s="0" t="n">
+        <v>1.512</v>
+      </c>
+      <c r="M72" s="0" t="n">
+        <v>0.088</v>
+      </c>
+      <c r="N72" s="0" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="O72" s="0" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="P72" s="0" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="Q72" s="0" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="Y72" s="0" t="n">
+        <v>-75.926</v>
+      </c>
+      <c r="Z72" s="0" t="n">
+        <v>-11.288</v>
+      </c>
+      <c r="AE72" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI72" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>0.163375547446333</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>0.0023977879868503</v>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>0.0137187466824647</v>
+      </c>
+      <c r="K73" s="0" t="n">
+        <v>8.52293418302902</v>
+      </c>
+      <c r="L73" s="0" t="n">
+        <v>1.48295451693214</v>
+      </c>
+      <c r="M73" s="0" t="n">
+        <v>0.110365626784113</v>
+      </c>
+      <c r="N73" s="0" t="n">
+        <v>1.4498504476483</v>
+      </c>
+      <c r="O73" s="0" t="n">
+        <v>2.07107551894728</v>
+      </c>
+      <c r="P73" s="0" t="n">
+        <v>0.18370745876058</v>
+      </c>
+      <c r="Q73" s="0" t="n">
+        <v>7.62754182284029</v>
+      </c>
+      <c r="Y73" s="0" t="n">
+        <v>-89.041</v>
+      </c>
+      <c r="Z73" s="0" t="n">
+        <v>-12.763</v>
+      </c>
+      <c r="AE73" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF73" s="0" t="n">
+        <v>0.0107134878633691</v>
+      </c>
+      <c r="AG73" s="0" t="n">
+        <v>2.56488469012499</v>
+      </c>
+      <c r="AH73" s="0" t="n">
+        <v>0.0401657668107341</v>
+      </c>
+      <c r="AI73" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <v>0.189389551039068</v>
+      </c>
+      <c r="H74" s="0" t="n">
+        <v>0.0191114029293714</v>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>0.0616053772076994</v>
+      </c>
+      <c r="K74" s="0" t="n">
+        <v>7.89434743421026</v>
+      </c>
+      <c r="L74" s="0" t="n">
+        <v>2.10493155229986</v>
+      </c>
+      <c r="M74" s="0" t="n">
+        <v>0.22843290142136</v>
+      </c>
+      <c r="N74" s="0" t="n">
+        <v>2.2993039327885</v>
+      </c>
+      <c r="O74" s="0" t="n">
+        <v>18.6876928930546</v>
+      </c>
+      <c r="P74" s="0" t="n">
+        <v>0.104292274312715</v>
+      </c>
+      <c r="Q74" s="0" t="n">
+        <v>10.802080260442</v>
+      </c>
+      <c r="S74" s="0" t="n">
+        <v>27.347</v>
+      </c>
+      <c r="Y74" s="0" t="n">
+        <v>-85.136</v>
+      </c>
+      <c r="Z74" s="0" t="n">
+        <v>-12.218</v>
+      </c>
+      <c r="AE74" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF74" s="0" t="n">
+        <v>0.0136803810290885</v>
+      </c>
+      <c r="AG74" s="0" t="n">
+        <v>3.376826628973</v>
+      </c>
+      <c r="AH74" s="0" t="n">
+        <v>0.0501513950053542</v>
+      </c>
+      <c r="AI74" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G75" s="0" t="n">
+        <v>0.160410675821434</v>
+      </c>
+      <c r="H75" s="0" t="n">
+        <v>0.0032433006041952</v>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>0.0107114344017018</v>
+      </c>
+      <c r="K75" s="0" t="n">
+        <v>8.83032090153328</v>
+      </c>
+      <c r="L75" s="0" t="n">
+        <v>0.920598577285501</v>
+      </c>
+      <c r="M75" s="0" t="n">
+        <v>0.08662352501668</v>
+      </c>
+      <c r="N75" s="0" t="n">
+        <v>1.73723820087858</v>
+      </c>
+      <c r="O75" s="0" t="n">
+        <v>2.23317605208635</v>
+      </c>
+      <c r="P75" s="0" t="n">
+        <v>0.172333779991541</v>
+      </c>
+      <c r="Q75" s="0" t="n">
+        <v>8.8898938853751</v>
+      </c>
+      <c r="S75" s="0" t="n">
+        <v>5.252</v>
+      </c>
+      <c r="Y75" s="0" t="n">
+        <v>-86.101</v>
+      </c>
+      <c r="Z75" s="0" t="n">
+        <v>-12.481</v>
+      </c>
+      <c r="AE75" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF75" s="0" t="n">
+        <v>0.0124023605296914</v>
+      </c>
+      <c r="AG75" s="0" t="n">
+        <v>2.36938356664775</v>
+      </c>
+      <c r="AH75" s="0" t="n">
+        <v>0.0460506709335277</v>
+      </c>
+      <c r="AI75" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="G76" s="0" t="n">
+        <v>0.0467166633663416</v>
+      </c>
+      <c r="H76" s="0" t="n">
+        <v>0.0102993751928283</v>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>0.107306699010177</v>
+      </c>
+      <c r="K76" s="0" t="n">
+        <v>4.07116792007254</v>
+      </c>
+      <c r="L76" s="0" t="n">
+        <v>0.455648037161756</v>
+      </c>
+      <c r="M76" s="0" t="n">
+        <v>0.0171492849957877</v>
+      </c>
+      <c r="N76" s="0" t="n">
+        <v>0.182482552111723</v>
+      </c>
+      <c r="O76" s="0" t="n">
+        <v>0.302194114131295</v>
+      </c>
+      <c r="P76" s="0" t="n">
+        <v>0.575673840047998</v>
+      </c>
+      <c r="Q76" s="0" t="n">
+        <v>1.00858708701716</v>
+      </c>
+      <c r="Y76" s="0" t="n">
+        <v>-110.886</v>
+      </c>
+      <c r="Z76" s="0" t="n">
+        <v>-15.606</v>
+      </c>
+      <c r="AE76" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF76" s="0" t="n">
+        <v>0.0066049392071814</v>
+      </c>
+      <c r="AG76" s="0" t="n">
+        <v>0.622071542902076</v>
+      </c>
+      <c r="AH76" s="0" t="n">
+        <v>0.0098863608096161</v>
+      </c>
+      <c r="AI76" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:B76">
+    <filterColumn colId="0" hiddenButton="1">
+      <filters>
+        <filter val="Wade"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="0" hiddenButton="1"/>
+  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6438,6 +11852,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11864,4 +17279,262 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="16.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.04"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.310526288452836</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.361980813179073</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.858941566800132</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.117381357762017</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.127532164929982</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.311310064011197</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.114725286867467</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.201120747249083</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.482012395003098</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.137331118412547</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.270041434547446</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.293645560855869</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.2685030063957</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.356769166134891</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1.49180709707671</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.182482552111723</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.302194114131295</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1.00858708701716</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>